--- a/questions_import.xlsx
+++ b/questions_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38482A70-327B-4FDA-ADA2-69CEA3B1D40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29871683-C8D1-447C-9FBE-E8B7C67086F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="343">
   <si>
     <t>question</t>
   </si>
@@ -1332,6 +1332,1352 @@
   </si>
   <si>
     <t xml:space="preserve">17-   مفيش اسالة اكمل </t>
+  </si>
+  <si>
+    <t>1- مؤسس سر الإفخارستيا هو</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "السيد المسيح ",
+                    "status": 1
+                },
+                {
+                    "answer": "بطرس الرسول",
+                    "status": 0
+                },
+                {
+                    "answer": "مرقس الرسول",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>2- 'الحكمة بنت بيتها نحتت أعمدتها السبعة' الشاهد أم (..... : .....)</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "١:٩ ",
+                    "status": 1
+                },
+                {
+                    "answer": "٨:٢ ",
+                    "status": 0
+                },
+                {
+                    "answer": "١٠:٢",
+                    "status": 0
+                },
+                {
+                    "answer": "١:٥",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>3- سمى آباء الكنيسة جرن المعمودية</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "باب الكنيسة ",
+                    "status": 0
+                },
+                {
+                    "answer": "بطن الكنيسة ",
+                    "status": 1
+                },
+                {
+                    "answer": " رأس الكنيسة",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>4- عدد رشومات الجسم كله بزيت الميرون</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "٣٦",
+                    "status": 1
+                },
+                {
+                    "answer": "٨٣ ",
+                    "status": 0
+                },
+                {
+                    "answer": "٥٠ ",
+                    "status": 0
+                },
+                {
+                    "answer": "٤٠ ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>5- تكون رسامة الكهنة في القداس بعد</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "المزامير ",
+                    "status": 0
+                },
+                {
+                    "answer": "صلاة الشكر ",
+                    "status": 0
+                },
+                {
+                    "answer": "صلاة الصلح",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>6- 'اشفوا مرضى طهروا برصاً. هذه الآية تدل على</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الميرون ",
+                    "status": 0
+                },
+                {
+                    "answer": "المعمودية ",
+                    "status": 0
+                },
+                {
+                    "answer": " مسحة المرضى",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>7- قال الرب يسوع 'قم احمل فراشك' للـ</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "المفلوج ",
+                    "status": 1
+                },
+                {
+                    "answer": " السامري  ",
+                    "status": 0
+                },
+                {
+                    "answer": "نازفة الدم",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>8- من إشارات المعمودية فى العهد القديم</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الطوفان ",
+                    "status": 1
+                },
+                {
+                    "answer": "شجرة الحياة ",
+                    "status": 0
+                },
+                {
+                    "answer": "لوحى الشريعة  ",
+                    "status": 0
+                },
+                {
+                    "answer": "مزامير داود ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>9- أحضر زيت الميرون إلى مصر</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "البابا أثناسيوس الرسولى ",
+                    "status": 0
+                },
+                {
+                    "answer": "البابا كيرلس عمود الدين ",
+                    "status": 0
+                },
+                {
+                    "answer": "مار مرقس الرسول",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>10-  فى طقس الإكليل يوضع الإكليل على رأس</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الرجل والمرأة ",
+                    "status": 1
+                },
+                {
+                    "answer": "المرأة فقط ",
+                    "status": 0
+                },
+                {
+                    "answer": "الرجل فقط",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>11- مؤسس كل الأسرار هم التلاميذ وسلموها إلى من بعدهم</t>
+  </si>
+  <si>
+    <t>12- يسمى سر الإفخارستيا بسر التناول وسر الأسرار</t>
+  </si>
+  <si>
+    <t>13- يتكون سر مسحة المرضى من 7 صلوات</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "صح",
+                    "status": 1
+                },
+                {
+                    "answer": "خطا ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>14- سر الاعتراف لا يوجد له زمن أو ميعاد محدد</t>
+  </si>
+  <si>
+    <t>15- سر المعمودية له المرتبة الثانية بعد الكهنوت لأنه باب يدخل منه المؤمن إلى الكنيسة وملكوت النعمة</t>
+  </si>
+  <si>
+    <t>1. يبدأ اليوم القبطى فى الغروب وينتهى فى الغروب</t>
+  </si>
+  <si>
+    <t>2. يمكن عمل قداس بدون رفع بخور باكر</t>
+  </si>
+  <si>
+    <t>3. يضع الكاهن خمس أيادى بخور فى بداية دورة البخور.</t>
+  </si>
+  <si>
+    <t>4. يفتح الكاهن ستر الهيكل من اليمين إلى الشمال</t>
+  </si>
+  <si>
+    <t>5. يصلى رفع بخور باكر وعشية داخل الهيكل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. يجب أن يكون قنديل الشرقية (حضن الآب) موقد دائماً </t>
+  </si>
+  <si>
+    <t>7. دُعِيَتْ أرباع الناقوص بهذا الاسم لأنها تُرَتَّل بمصاحبة الدف</t>
+  </si>
+  <si>
+    <t>8. فى الأديرة تُضَاف صلاة النوم بعد صلوات الأجبية</t>
+  </si>
+  <si>
+    <t>9. يقول الكاهن إشليل إيـﭭلوجيسون فى حالة وجود كاهن شريك فى صلاة الشكر</t>
+  </si>
+  <si>
+    <t>10. فى صوم نينوى لا يُرْفَع بخور عشية</t>
+  </si>
+  <si>
+    <t>11. كان مذبخ البخور فى العهد القديم داخل قدس الأقداس</t>
+  </si>
+  <si>
+    <t>12. يخرج الكاهن من الهيكل برجله اليمني دليل القوى</t>
+  </si>
+  <si>
+    <t>13. يتم ممارسة صلوات دورة البخور سراً</t>
+  </si>
+  <si>
+    <t>14. تُصلى أوشية الراقدين في رفع بخور باكر يوم السبت</t>
+  </si>
+  <si>
+    <t>15. أيادي البخور في دورة البخور ترمز إلى جراحات السيد المسيح الخمسة</t>
+  </si>
+  <si>
+    <t>16. يُصلي الكاهن أوشية القرابين امام المذبح في الهيكل</t>
+  </si>
+  <si>
+    <t>17. معظم مردات الشماس تُصلى باللغه اليونانية</t>
+  </si>
+  <si>
+    <t>18. زكريا و هارون من رجال العهد القديم الذين قبلت تقدماتهم</t>
+  </si>
+  <si>
+    <t>19. تغيير سؤال اكمكل الصورة</t>
+  </si>
+  <si>
+    <t>1. يرتب الجزء الأول فى القداس )صلاة الاستعداد، ارتداء ملابس الخدمة، صلاة المزامير، غسل الأيدى، تقديم الحمل</t>
+  </si>
+  <si>
+    <t>2. من أسماء القداس 'أنافورا ' وتعنى قبول نعمة</t>
+  </si>
+  <si>
+    <t>3. فى عيد العنصرة يُصَّلى مزامير صلاة الساعة الثالثة فقط</t>
+  </si>
+  <si>
+    <t>4. عدد اصحاحات رسائل بولس الرسول التى كتبها  100 أصحاح</t>
+  </si>
+  <si>
+    <t>5.   أثناء إرتداء ملابس الخدمة 'التونية' يُصَّلى المزمور 29 ، 92</t>
+  </si>
+  <si>
+    <t>6. الأربع أفعال الأساسية فى 'الإفخارستيا' القداس هى أخذ وبارك وكسر وأعطى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. الآية الدالة على مواظبة التلاميذ على كسر الخبز هي ' وأما الأمور الباقية فعندما أجىء أرتبها' </t>
+  </si>
+  <si>
+    <t>8- قداس يُصَلَّي به فى الأعياد السيدية والفرح</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الباسيبلى ",
+                    "status": 0
+                },
+                {
+                    "answer": "الكيرلسى ",
+                    "status": 0
+                },
+                {
+                    "answer": "الغريغورى",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>9- القداسات التى لا يُصَلَّي فيها مزامير هي:</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "قداس عيد الميلاد ، قداس عيد القيامة ، قداس عيد الغطاس",
+                    "status": 0
+                },
+                {
+                    "answer": "قداس عيد الميلاد ، قداس عيد القيامة ، قداس عيد الغطاس ، قداس خميس العهد ",
+                    "status": 1
+                },
+                {
+                    "answer": " قداس عيد الميلاد ، قداس عيد القيامة ، قداس عيد العنصرة ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>10- أثناء غسل الكاهن يده يقول مزامير:</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": " 50: 7 ، 25: 6-7    ",
+                    "status": 1
+                },
+                {
+                    "answer": "150: 7 ، 25: 9-10   ",
+                    "status": 0
+                },
+                {
+                    "answer": " 50: 6-7  ، 25: 7 ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>11-  من أسماء القداس:</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": " ليتورجيا ، قطمارس ، أنافورا",
+                    "status": 0
+                },
+                {
+                    "answer": "قداس ، أنافورا ، إفخارستيا",
+                    "status": 1
+                },
+                {
+                    "answer": " أنافور ، إبروسفورا ، إبصالموص  ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>12- قبل أن يبدأ الكاهن بطقس تقديم الحمل يجب أن يتأكد من وجود</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": " قربان الحمل، اللوح المقدس،  قارورة الأباركة، ملابس الخدمة",
+                    "status": 0
+                },
+                {
+                    "answer": " قربان الحمل، القطمارس، قارورة الأباركة، ملابس الخدمة ",
+                    "status": 0
+                },
+                {
+                    "answer": " قربان الحمل، قارورة الأباركة، ملابس الخدمة، أبريق الماء  ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>13- تُسَمَّى أوشية التقدمة بأوشية:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": " اللفائف ",
+                    "status": 0
+                },
+                {
+                    "answer": " الغطاء  ",
+                    "status": 1
+                },
+                {
+                    "answer": " الأوانى   ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>14- تستخدم الكنيسة 5 قطمارسات على مدار السنة:</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": " قطمارس أيام وقطمارس آحاد وقطمارس شعانين وقطمارس صوم كبير وقطمارس الخمسين",
+                    "status": 0
+                },
+                {
+                    "answer": " قطمارس أيام وقطمارس آحاد وقطمارس أسبوع الآلام وقطمارس صوم كبير وقطمارس الخمسين",
+                    "status": 1
+                },
+                {
+                    "answer": " قطمارس أيام وقطمارس آحاد وقطمارس أسبوع الآلام وقطمارس كيهكى  وقطمارس الخمسين",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>15- فى حالة وجود خادم شريك فى القداس مع الكاهن الخديم، الذي يقول تحليل الخدام هو</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": " الكاهن الخديم",
+                    "status": 0
+                },
+                {
+                    "answer": " الكاهن الخديم ",
+                    "status": 1
+                },
+                {
+                    "answer": " الاثنان معا ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- معني كلمة  أنافورا </t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "القرابين ",
+                    "status": 0
+                },
+                {
+                    "answer": "الصعيدة ",
+                    "status": 1
+                },
+                {
+                    "answer": "الذكري",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>2-  معني كلمة أسبازموس</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "مديح ",
+                    "status": 0
+                },
+                {
+                    "answer": "أفراح ",
+                    "status": 0
+                },
+                {
+                    "answer": "تقبيل ",
+                    "status": 1
+                },
+                {
+                    "answer": "كل ما سبق ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>3- عند قول الكاهن ........................................ يضع يد بخور فى الشورية إشارة إلى التجسد</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "لأنه في كل مرة ",
+                    "status": 0
+                },
+                {
+                    "answer": "لأنه فيما هو راسم",
+                    "status": 1
+                },
+                {
+                    "answer": "تجسد وتأنس وعلمنا طرق الخلاص",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>4- حركة استبدال الكاهن اللفائف التي علي يده ببعضها ترمز إلي</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "حركة الشاروبيم ",
+                    "status": 0
+                },
+                {
+                    "answer": "حركة أجنحة الملائكة ",
+                    "status": 1
+                },
+                {
+                    "answer": "حركة الحمام ",
+                    "status": 0
+                },
+                {
+                    "answer": "كل ما سبق",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>5- ينير الشماس الشموع في القداس أثناء</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "اختيار الحمل ",
+                    "status": 0
+                },
+                {
+                    "answer": " التقديس والقسمة ",
+                    "status": 0
+                },
+                {
+                    "answer": " التناول ",
+                    "status": 0
+                },
+                {
+                    "answer": " كل ماسبق ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>6- يقسم الكاهن الجسد إلى</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "ثلث وثلثين ",
+                    "status": 1
+                },
+                {
+                    "answer": "ثلث وثلث ",
+                    "status": 0
+                },
+                {
+                    "answer": " نصف وثلث ",
+                    "status": 0
+                },
+                {
+                    "answer": " كل ماسبق",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>7- فى صلوات الاستدعاء فى القداس الباسيلى يأمر الشماس الشعب للسجود قائلاً 'اسجدوا لله بخوف ورعدة' وفى القداس الغريغورى تستبدل بـ</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "اسجدوا لله بقوة ورعدة ",
+                    "status": 0
+                },
+                {
+                    "answer": "اسجدوا لله برعدة وخوف ",
+                    "status": 0
+                },
+                {
+                    "answer": " اسجدوا للحمل كلمة الله ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>8- يرشم الكاهن في قطعه أجيوس ثلاث مرات بعلامة الصليب بهذا الترتيب</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "أول مرة علي ذاته ثم علي خدام المذبح ثم علي الشعب",
+                    "status": 1
+                },
+                {
+                    "answer": "أول مرة علي الشعب ثم علي ذاته ثم علي خدام المذبح ",
+                    "status": 0
+                },
+                {
+                    "answer": "أول مرة علي خدام المذبح ثم علي الشعب ثم علي ذاته",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>9- تدور صلاة الصلح حول محورين هما</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "فداء المسيح وقبلة المصالحة. ",
+                    "status": 0
+                },
+                {
+                    "answer": "السلام الذي صنعه الله ليصالحنا معه وطلب الاستحقاق أن يقبل المؤمنين بعضهم بعضاً بقبلة طاهرة  ",
+                    "status": 1
+                },
+                {
+                    "answer": "تجسد المسيح وقبلة المصالحة",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>10- قطعة أجيوس فى القداس الباسيلى تحكى عن:</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "قصة السقوط وتدبير الخلاص",
+                    "status": 1
+                },
+                {
+                    "answer": "غير موصوفة هي حكمة الله.",
+                    "status": 0
+                },
+                {
+                    "answer": "لاحدود لمحبة الله.",
+                    "status": 0
+                },
+                {
+                    "answer": "كل ما سبق.",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>11- الأسبازموس الآدام الشهير في القداس هو 'الشاروبيم يسجدون لك'</t>
+  </si>
+  <si>
+    <t>12- يطلب الكاهن أن يحل الروح القدس على الشعب أولاً ثم على القرابين</t>
+  </si>
+  <si>
+    <t>13- يدور الكاهن بإصبعه علي حافة الكأس مرة عكس عقارب الساعة ومرة أخري مع عقارب الساعة</t>
+  </si>
+  <si>
+    <t>14- تنقسم صلوات التقديس في القداس إلي أربعة أقسام (التأسيس-الذكري-الاستدعاء-الشكر)</t>
+  </si>
+  <si>
+    <t>15- الأسبازموس الواطس الشهير في القداس هو 'افرحي يامريم'</t>
+  </si>
+  <si>
+    <t>1. الأجبية تعني ساعة وهي كلمة معربة من اللفظ القبطي</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "وجب ",
+                    "status": 0
+                },
+                {
+                    "answer": "أجب ",
+                    "status": 1
+                },
+                {
+                    "answer": " يجب",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>2. تحتوي الأجبية علي عدد ....... من المزامير.</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "97",
+                    "status": 0
+                },
+                {
+                    "answer": "77",
+                    "status": 1
+                },
+                {
+                    "answer": "87",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>3. تبدأ تسبحة عشية بلحن للمزمور .......</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "149",
+                    "status": 0
+                },
+                {
+                    "answer": "116",
+                    "status": 1
+                },
+                {
+                    "answer": "119",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>4. يُعْرَف سفر المزامير في العبرية باسم تهليم وتعني .......</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "غَنَّي ",
+                    "status": 1
+                },
+                {
+                    "answer": "أنشد ",
+                    "status": 0
+                },
+                {
+                    "answer": "الحمد والتسبيح ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>5. المزامير اليتيمة هي التي تُنْسَبْ إلي</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "قورح ",
+                    "status": 0
+                },
+                {
+                    "answer": "  هيمان الأزراحي ",
+                    "status": 0
+                },
+                {
+                    "answer": "لا تُنْسَبْ إلي أحد",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>6. لكل ساعة من سواعي الأجبية عدد .......   مزمور</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "12",
+                    "status": 1
+                },
+                {
+                    "answer": " 15",
+                    "status": 0
+                },
+                {
+                    "answer": " 17 ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>7. صلاة .......   نجد أن لها 19 مزموراً</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "نصف الليل",
+                    "status": 0
+                },
+                {
+                    "answer": "باكر ",
+                    "status": 1
+                },
+                {
+                    "answer": " الستار ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>8. الهوس الثاني هو المزمور.......</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "148 ",
+                    "status": 0
+                },
+                {
+                    "answer": "150 ",
+                    "status": 0
+                },
+                {
+                    "answer": "135",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>9. يُقال المزمور في الأعياد السيدية باللحن .......</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الشامي ",
+                    "status": 0
+                },
+                {
+                    "answer": " الإدريبي ",
+                    "status": 0
+                },
+                {
+                    "answer": "السنجاري",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>10. يُقال المزمور باللحن .......  في أسبوع الآلام</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الشامي ",
+                    "status": 0
+                },
+                {
+                    "answer": " الإدريبي ",
+                    "status": 1
+                },
+                {
+                    "answer": "السنجاري",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>11. يُقْرَأ سفر المزامير كاملاً في</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "جمعه ختام الصوم وتجليس البطريرك ",
+                    "status": 0
+                },
+                {
+                    "answer": " ختام صلوات الجمعة العظيمة ونياحة البطريرك أو الأسقف ",
+                    "status": 1
+                },
+                {
+                    "answer": " ختام صوم نينوي",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>12. قبل تسبحة عشية لا تُصَلَّي المزامير في</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "أيام الصوم الكبير ",
+                    "status": 0
+                },
+                {
+                    "answer": " صوم نينوي ",
+                    "status": 0
+                },
+                {
+                    "answer": "عيد البشارة والصليب ",
+                    "status": 0
+                },
+                {
+                    "answer": "كل ماسبق",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>13. قام بتكملة تسبحة الملائكة البابا</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "ديمتريوس ",
+                    "status": 0
+                },
+                {
+                    "answer": "أثناسيوس ",
+                    "status": 1
+                },
+                {
+                    "answer": " سانتيوس",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>14.   تذكرنا  صلاة نصف الليل بـ</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "قيامة السيد المسيح ",
+                    "status": 0
+                },
+                {
+                    "answer": " السهر والاستعداد ",
+                    "status": 1
+                },
+                {
+                    "answer": "حلول الروح القدس",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>15.   في ختام صلوات المزامير نختم بـ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "كيرياليسون 41 مره ",
+                    "status": 0
+                },
+                {
+                    "answer": " إرحمنا يا الله ثم إرحمنا ",
+                    "status": 1
+                },
+                {
+                    "answer": "مزمور التوبة",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>16.  القطعة الثالثة في صلوات السواعي تختص بالروح القدس</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "صح",
+                    "status": 0
+                },
+                {
+                    "answer": " خطا ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>17.  كل أنواع الصلوات في الطقس القبطي بدون استثناء تبدأ بطلب رحمة الرب</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "صح",
+                    "status": 1
+                },
+                {
+                    "answer": " خطا ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>18. صلاة الشكر هي صلاة ليتورچية حديثة في المسيحية</t>
+  </si>
+  <si>
+    <t>19. نصلي كيرياليسون 41 مرة إشارة لعدد الجلدات التي جُلد بها المسيح</t>
+  </si>
+  <si>
+    <t>20. نصلي في صلاة باكر جزء من رسالة بولس الرسول إلى أهل أفسس (1 : 4-5)</t>
+  </si>
+  <si>
+    <t>1. كلمة هوس هي كلمة يونانية تعني تسبحة</t>
+  </si>
+  <si>
+    <t>2. يقال لحن تين ناف أثناء الفترة من عيد القيامة إلى آخر هاتور</t>
+  </si>
+  <si>
+    <t>3. الهوس الثالث مأخوذ من تَتِمَّة سِفر دانيال</t>
+  </si>
+  <si>
+    <t>4. الهوس الثالث يتمحور حول رحمة الله الدائمة</t>
+  </si>
+  <si>
+    <t>5. الهوس الأول كتبه</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "هارون أخو موسى النبى ",
+                    "status": 0
+                },
+                {
+                    "answer": "موسى النبى ",
+                    "status": 1
+                },
+                {
+                    "answer": "سليمان الملك",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>6.مَن أدخَل نظام الأنتيفون في التسبيح هو</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "عزاريا ",
+                    "status": 0
+                },
+                {
+                    "answer": " حنانيا ",
+                    "status": 0
+                },
+                {
+                    "answer": " نحميا ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>7.يُعتَبَر التسبيح أرقى أنواع الصلاة لأنه</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "عمل الملايكة  ",
+                    "status": 0
+                },
+                {
+                    "answer": "تسبيح وشكر لله دون غرض آخر ",
+                    "status": 1
+                },
+                {
+                    "answer": "لا نقدر أن نعيش بدونه ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>8- لماذا التسبيح في نصف الليل؟</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "بسبب الهدوء ",
+                    "status": 0
+                },
+                {
+                    "answer": "تكون الكنيسة فى حالة سهر انتظاراً للمسيح مثل العذاري الحكيمات",
+                    "status": 1
+                },
+                {
+                    "answer": "لعمل القداس باكراً بعد التسبحة",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>9- الفرق بين كتابيّ الإبصلمودية السنوية والكيهكية هو</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الإبصلمودية الكيهكية بها الهوس الكيهكى زيادة فقط  ",
+                    "status": 0
+                },
+                {
+                    "answer": " لا يوجد فرق ",
+                    "status": 0
+                },
+                {
+                    "answer": "الإبصلمودية الكيهكية بها الهوس الكبير وابصاليات وطروحات ومدائح",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>10-وصل</t>
+  </si>
+  <si>
+    <t>1. تُصَلَّي أوشية الراقدين في عشيات كل الأيام ما عدا الأعياد السيدية</t>
+  </si>
+  <si>
+    <t>2. يُحْتَفل بتذكار أعياد البشارة والميلاد والقيامة في يوم 29 من كل شهر قبطي</t>
+  </si>
+  <si>
+    <t>3. يُصَلَّي لحن 'إنثو تيه تي شوري' في أيام صوم الميلاد</t>
+  </si>
+  <si>
+    <t>4. إذا وقع عيد البشارة يوم سبت لعازر حينئذ يُصَلَّي بالطقس الفرايحي</t>
+  </si>
+  <si>
+    <t>5. لا تُصَـلَّي مزامير السواعي في قداس عيد الميلاد بل رفع الحمل مباشرة</t>
+  </si>
+  <si>
+    <t>6. عيد الختان هو أحد الأعياد السيدية الكبري</t>
+  </si>
+  <si>
+    <t>7. يبدأ تاريخ تقويم الشهداء من عصر الإمبراطور نيرون</t>
+  </si>
+  <si>
+    <t>8. يُصَلَّي بالطقس الفرايحي من أول 1 توت إلي 17 توت</t>
+  </si>
+  <si>
+    <t>9. نصوم يوميّ الأربعاء والجمعة دائماً حتي لو جاء فيهما عيديّ الميلاد والغطاس</t>
+  </si>
+  <si>
+    <t>10. في السنة الكبيسة يتم الاحتفال بعيد الميلاد يوميّ 28، 29 كيهك</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "صح",
+                    "status": 1
+                },
+                {
+                    "answer": " خطا ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>11. في سبوت وآحاد شهر كيهك نصلي سواعي الثالثة والسادسة والتاسعة</t>
+  </si>
+  <si>
+    <t>12. لا تتكرر قراءات فصول برمون الغطاس حتي لو جاء 3 أيام</t>
+  </si>
+  <si>
+    <t>13.  فصول صوم نينوي من قطمارس الصوم الكبير</t>
+  </si>
+  <si>
+    <t>14. نصلي أول أيام الصوم الكبير وجمعة ختام الصوم بالطقس السنوي</t>
+  </si>
+  <si>
+    <t>15. إذا جاء عيد دخول السيد المسيح إلي الهيكل يوم أحد في الصوم الكبير تُقرأ فصول يوم الأحد</t>
+  </si>
+  <si>
+    <t>16. نصلي صلوات برمون الميلاد بالطقس</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الكيهكي ",
+                    "status": 0
+                },
+                {
+                    "answer": " السنوي  ",
+                    "status": 1
+                },
+                {
+                    "answer": "الفرايحي ",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>17. نحتفل بعيد الغطاس يوم</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "11 طوبة  ",
+                    "status": 0
+                },
+                {
+                    "answer": " 12 طوبة   ",
+                    "status": 0
+                },
+                {
+                    "answer": "11، 12 طوبة ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>18. من برمون الميلاد إلي عيد الختان نقول</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "آكتشي أومس ",
+                    "status": 0
+                },
+                {
+                    "answer": " آك طونك   ",
+                    "status": 0
+                },
+                {
+                    "answer": "آڤ ماسك",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>19. إذا جاء عيد الغطاس يوم الاثنين يكون البرمون</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "يوم واحد ",
+                    "status": 0
+                },
+                {
+                    "answer": " يومان   ",
+                    "status": 0
+                },
+                {
+                    "answer": "ثلاثة أيام",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>20. في سبوت وآحاد الصوم الكبير نصلي سواعي</t>
+  </si>
+  <si>
+    <t>[
+                {
+                    "answer": "الثالثة والسادسة ",
+                    "status": 1
+                },
+                {
+                    "answer": " الثالثة والسادسة والتاسعة    ",
+                    "status": 0
+                },
+                {
+                    "answer": "الـ 5 سواعي",
+                    "status": 0
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>1. في طقس رسامة الرهبان يُصَلَّي المزمور والإنجيل باللحن الأدريبي فيما عدا الآحاد والخمسين المقدسة يُصَلَّي باللحن الفرايحي</t>
+  </si>
+  <si>
+    <t>2. يتم رسامة الأرشي دياكون برشم الجبهة</t>
+  </si>
+  <si>
+    <t>3. إذا تمت رسامة الدياكون والأرشي دياكون قبل الزواج فلا يتزوج</t>
+  </si>
+  <si>
+    <t>4. كلمة (إبصالتس) تعني قارئ بينما كلمة أغنسطس تعني (مرتل)</t>
+  </si>
+  <si>
+    <t>5. شرط لمن يصير راهباً أن يقيم في الدير سنة يتعلم فيها الرهبنة</t>
+  </si>
+  <si>
+    <t>6. عند رسامة الأغنسطس يُقَصْ شعره 5 قصات رمز لجراحات المسيح</t>
+  </si>
+  <si>
+    <t>7. طقس تكريس المكرسات يتم بوضع اليد</t>
+  </si>
+  <si>
+    <t>8. يتقدم المرشح لدرجة القسيسية وهو لابس ملابس الشماس والزنار علي كتفه اليمين</t>
+  </si>
+  <si>
+    <t>9. يتم استقبال الكاهن الجديد عند دخوله الكنيسة بزفة وهو ممسكاً بالإنجيل</t>
+  </si>
+  <si>
+    <t>10. في طقس حل الزنار للشمامسة نصلي لحن تي شوري</t>
+  </si>
+  <si>
+    <t>11. يجب أن يكون المرشح لدرجة الإيبودياكون ملماً بجميع طقوس الكنيسة وألحانها والوظائف الشماسية</t>
+  </si>
+  <si>
+    <t>12. في طقس تكريس الرهبان تُقال النبوات بعد المزمور الخمسون</t>
+  </si>
+  <si>
+    <t>13. يتم تغطية المتقدم للرهبنة بستر كأنه ميت</t>
+  </si>
+  <si>
+    <t>14. من شروط رسامة الأرشي دياكون أن لا يقل سنه عن 38 سنة</t>
+  </si>
+  <si>
+    <t>15. كلمة (قمص) أو (إيغومانوس) مأخوذة من الكملة القبطية وتعني مدبر</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+                {
+                    "answer": "صح",
+                    "status": 0
+                },
+                {
+                    "answer": " خطا ",
+                    "status": 1
+                }
+            ]</t>
+  </si>
+  <si>
+    <t>16. ينام الأخ المراد رهبنته أمام الهيكل علي ظهره ورأسه للشرق ورجلاه للغرب واضعاً يديه علي صدره</t>
+  </si>
+  <si>
+    <t>17. الشئ المشترك في رسامة الأغنسطس وتكريس الراهبات هو قص الشعر</t>
+  </si>
+  <si>
+    <t>18. طقس رسامة الشمامسة والقس والق\مص وتكريس الرهبان والراهبات يتم بعد صلاة الصلح</t>
+  </si>
+  <si>
+    <t>19. يُقال لحن (بي إبنيڤما) في طقس رسامة القس والقمص</t>
+  </si>
+  <si>
+    <t>20. ينفخ الأسقف في فم الكاهن الجديد نفخة الروح القدس بعد الانتهاء من القداس الإلهي</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +3133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAA58B4-CCC6-449D-B1B2-34A66B80EAA5}">
-  <dimension ref="A1:D194"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" customWidth="1"/>
@@ -1812,2745 +3158,1895 @@
     </row>
     <row r="2" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
+        <v>151</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="A5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
+      <c r="A6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
+        <v>163</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
+      <c r="A9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1</v>
+        <v>169</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>170</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1</v>
+        <v>171</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1</v>
+        <v>172</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
+        <v>173</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
+        <v>175</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
+        <v>176</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1</v>
+        <v>178</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="1">
-        <v>1</v>
+        <v>179</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1</v>
+        <v>181</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
+        <v>182</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1</v>
+        <v>183</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
+      <c r="A24" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1</v>
+        <v>185</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1</v>
+        <v>187</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1</v>
+        <v>188</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
+        <v>189</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1</v>
+      <c r="A30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1</v>
+      <c r="A31" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1</v>
+        <v>194</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D38">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D39">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1</v>
+        <v>200</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1</v>
+        <v>203</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1</v>
+      <c r="A45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45">
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1</v>
+      <c r="A46" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1</v>
+        <v>211</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1</v>
+        <v>213</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
+        <v>215</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B51" s="1">
-        <v>1</v>
+        <v>219</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>63</v>
+        <v>222</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1</v>
+        <v>223</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>224</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B54" s="1">
-        <v>1</v>
+      <c r="A54" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="1">
-        <v>1</v>
+        <v>227</v>
+      </c>
+      <c r="B55">
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
+        <v>229</v>
+      </c>
+      <c r="B56">
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="1">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>232</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1</v>
+        <v>233</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1</v>
+        <v>235</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="1">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1</v>
+        <v>239</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
+        <v>241</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>242</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>243</v>
+      </c>
+      <c r="B65">
+        <v>3</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
+        <v>244</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>245</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
+      <c r="A67" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
+        <v>248</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>250</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1</v>
+        <v>252</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1</v>
+        <v>254</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>76</v>
+        <v>255</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="1">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1">
-        <v>1</v>
+      <c r="A73" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1</v>
+      <c r="A74" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74">
+        <v>3</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="1">
-        <v>1</v>
+        <v>262</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B76" s="1">
-        <v>1</v>
+      <c r="A76" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B77" s="1">
-        <v>1</v>
+      <c r="A77" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="D77">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B78" s="1">
-        <v>1</v>
+        <v>268</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>90</v>
+        <v>269</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1</v>
+        <v>270</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>92</v>
+        <v>271</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B80" s="1">
-        <v>1</v>
+        <v>272</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>94</v>
+        <v>273</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B81" s="1">
-        <v>1</v>
+        <v>274</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D81">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B82" s="1">
-        <v>1</v>
+        <v>276</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B83" s="1">
-        <v>1</v>
+        <v>278</v>
+      </c>
+      <c r="B83">
+        <v>3</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B84" s="1">
-        <v>1</v>
+        <v>279</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="D84">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="1">
-        <v>1</v>
+        <v>280</v>
+      </c>
+      <c r="B85">
+        <v>3</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B86" s="1">
-        <v>1</v>
+        <v>281</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B87" s="1">
-        <v>1</v>
+        <v>282</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="D87">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B88" s="1">
-        <v>1</v>
+        <v>283</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B89" s="1">
-        <v>1</v>
+        <v>284</v>
+      </c>
+      <c r="B89">
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B90" s="1">
-        <v>1</v>
+        <v>285</v>
+      </c>
+      <c r="B90">
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>96</v>
+        <v>286</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B91" s="1">
-        <v>1</v>
+        <v>287</v>
+      </c>
+      <c r="B91">
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>113</v>
+        <v>288</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B92" s="1">
-        <v>1</v>
+        <v>289</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>96</v>
+        <v>290</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B93" s="1">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="B93">
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>96</v>
+        <v>292</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B94" s="1">
-        <v>1</v>
+        <v>293</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" s="1">
-        <v>1</v>
+        <v>295</v>
+      </c>
+      <c r="B95">
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B96" s="1">
-        <v>1</v>
+      <c r="A96" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B97" s="1">
-        <v>1</v>
+      <c r="A97" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>88</v>
+        <v>275</v>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B98" s="1">
-        <v>1</v>
+        <v>298</v>
+      </c>
+      <c r="B98">
+        <v>3</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>90</v>
+        <v>275</v>
       </c>
       <c r="D98">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1</v>
+        <v>299</v>
+      </c>
+      <c r="B99">
+        <v>3</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1</v>
+        <v>300</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1</v>
+        <v>301</v>
+      </c>
+      <c r="B101">
+        <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B102" s="1">
-        <v>1</v>
+        <v>302</v>
+      </c>
+      <c r="B102">
+        <v>3</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B103" s="1">
-        <v>1</v>
+        <v>303</v>
+      </c>
+      <c r="B103">
+        <v>3</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B104" s="1">
-        <v>1</v>
+        <v>304</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B105" s="1">
-        <v>1</v>
+        <v>305</v>
+      </c>
+      <c r="B105">
+        <v>3</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B106" s="1">
-        <v>1</v>
+        <v>307</v>
+      </c>
+      <c r="B106">
+        <v>3</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B107" s="1">
-        <v>1</v>
+        <v>308</v>
+      </c>
+      <c r="B107">
+        <v>3</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="D107">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B108" s="1">
-        <v>1</v>
+        <v>309</v>
+      </c>
+      <c r="B108">
+        <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>110</v>
+        <v>277</v>
       </c>
       <c r="D108">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B109" s="1">
-        <v>1</v>
+        <v>310</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="D109">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="1">
-        <v>1</v>
+        <v>311</v>
+      </c>
+      <c r="B110">
+        <v>3</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111" s="1">
-        <v>1</v>
+        <v>312</v>
+      </c>
+      <c r="B111">
+        <v>3</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>113</v>
+        <v>313</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B112" s="1">
-        <v>1</v>
+        <v>314</v>
+      </c>
+      <c r="B112">
+        <v>3</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="D112">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B113" s="1">
-        <v>1</v>
+        <v>316</v>
+      </c>
+      <c r="B113">
+        <v>3</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>96</v>
+        <v>317</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B114" s="1">
-        <v>1</v>
+        <v>318</v>
+      </c>
+      <c r="B114">
+        <v>3</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>96</v>
+        <v>319</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B115" s="1">
-        <v>1</v>
+        <v>320</v>
+      </c>
+      <c r="B115">
+        <v>3</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="D115">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B116" s="1">
-        <v>1</v>
+      <c r="A116" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="D116">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B117" s="1">
-        <v>1</v>
+      <c r="A117" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>88</v>
+        <v>277</v>
       </c>
       <c r="D117">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B118" s="1">
-        <v>1</v>
+        <v>324</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>90</v>
+        <v>277</v>
       </c>
       <c r="D118">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B119" s="1">
-        <v>1</v>
+        <v>325</v>
+      </c>
+      <c r="B119">
+        <v>3</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c r="D119">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B120" s="1">
-        <v>1</v>
+        <v>326</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>94</v>
+        <v>275</v>
       </c>
       <c r="D120">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B121" s="1">
-        <v>1</v>
+        <v>327</v>
+      </c>
+      <c r="B121">
+        <v>3</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="D121">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B122" s="1">
-        <v>1</v>
+        <v>328</v>
+      </c>
+      <c r="B122">
+        <v>3</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B123" s="1">
-        <v>1</v>
+        <v>329</v>
+      </c>
+      <c r="B123">
+        <v>3</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="D123">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B124" s="1">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="D124">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B125" s="1">
-        <v>1</v>
+        <v>331</v>
+      </c>
+      <c r="B125">
+        <v>3</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="D125">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B126" s="1">
-        <v>1</v>
+        <v>332</v>
+      </c>
+      <c r="B126">
+        <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B127" s="1">
-        <v>1</v>
+        <v>333</v>
+      </c>
+      <c r="B127">
+        <v>3</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="D127">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B128" s="1">
-        <v>1</v>
+        <v>334</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>110</v>
+        <v>277</v>
       </c>
       <c r="D128">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B129" s="1">
-        <v>1</v>
+        <v>335</v>
+      </c>
+      <c r="B129">
+        <v>3</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B130" s="1">
-        <v>1</v>
+        <v>336</v>
+      </c>
+      <c r="B130">
+        <v>3</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="D130">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B131" s="1">
-        <v>1</v>
+        <v>338</v>
+      </c>
+      <c r="B131">
+        <v>3</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>113</v>
+        <v>275</v>
       </c>
       <c r="D131">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B132" s="1">
-        <v>1</v>
+        <v>339</v>
+      </c>
+      <c r="B132">
+        <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="D132">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B133" s="1">
-        <v>1</v>
+        <v>340</v>
+      </c>
+      <c r="B133">
+        <v>3</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="D133">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B134" s="1">
-        <v>1</v>
+        <v>341</v>
+      </c>
+      <c r="B134">
+        <v>3</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>96</v>
+        <v>306</v>
       </c>
       <c r="D134">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B135" s="1">
-        <v>1</v>
+        <v>342</v>
+      </c>
+      <c r="B135">
+        <v>3</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>119</v>
+        <v>275</v>
       </c>
       <c r="D135">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B136" s="1">
-        <v>1</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D136">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B137" s="1">
-        <v>1</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D137">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B138" s="1">
-        <v>1</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D138">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B139" s="1">
-        <v>1</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D139">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B140" s="1">
-        <v>1</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D140">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B141" s="1">
-        <v>1</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D141">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B142" s="1">
-        <v>1</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D142">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B143" s="1">
-        <v>1</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D143">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B144" s="1">
-        <v>1</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D144">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B145" s="1">
-        <v>1</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D145">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B146" s="1">
-        <v>1</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D146">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B147" s="1">
-        <v>1</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D147">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B148" s="1">
-        <v>1</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D148">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B149" s="1">
-        <v>1</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D149">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B150" s="1">
-        <v>1</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D150">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B151" s="1">
-        <v>1</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D151">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B152" s="1">
-        <v>1</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D152">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B153" s="1">
-        <v>1</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D153">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B154" s="1">
-        <v>1</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D154">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B155" s="1">
-        <v>1</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D155">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B156" s="1">
-        <v>1</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D156">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B157" s="1">
-        <v>1</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D157">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B158" s="1">
-        <v>1</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D158">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B159" s="1">
-        <v>1</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D159">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B160" s="1">
-        <v>1</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D160">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B161" s="1">
-        <v>1</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D161">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B162" s="1">
-        <v>1</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D162">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B163" s="1">
-        <v>1</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D163">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B164" s="1">
-        <v>1</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D164">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B165" s="1">
-        <v>1</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D165">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B166" s="1">
-        <v>1</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D166">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B167" s="1">
-        <v>1</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D167">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B168" s="1">
-        <v>1</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D168">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B169" s="1">
-        <v>1</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D169">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B170" s="1">
-        <v>1</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D170">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B171" s="1">
-        <v>1</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D171">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B172" s="1">
-        <v>1</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D172">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B173" s="1">
-        <v>1</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D173">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B174" s="1">
-        <v>1</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D174">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B175" s="1">
-        <v>1</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D175">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B176" s="1">
-        <v>1</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D176">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B177" s="1">
-        <v>1</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D177">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B178" s="1">
-        <v>1</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D178">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B179" s="1">
-        <v>1</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D179">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B180" s="1">
-        <v>1</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D180">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B181" s="1">
-        <v>1</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D181">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B182" s="1">
-        <v>1</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D182">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B183" s="1">
-        <v>1</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D183">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B184" s="1">
-        <v>1</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D184">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B185" s="1">
-        <v>1</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D185">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B186" s="1">
-        <v>1</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D186">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B187" s="1">
-        <v>1</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D187">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B188" s="1">
-        <v>1</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D188">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B189" s="1">
-        <v>1</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D189">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B190" s="1">
-        <v>1</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D190">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B191" s="1">
-        <v>1</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D191">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B192" s="1">
-        <v>1</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D192">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B193" s="1">
-        <v>1</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D193">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B194" s="1">
-        <v>1</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D194">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A24" r:id="rId1" xr:uid="{EC0A32D8-DF6A-4D72-AD75-AA06C555A6C9}"/>
-    <hyperlink ref="A30" r:id="rId2" xr:uid="{5C3D0804-5699-4DBF-B411-3C3A412B89AE}"/>
-    <hyperlink ref="A31" r:id="rId3" xr:uid="{F5980D0F-FAAA-4535-9BE9-1508C15687DF}"/>
-    <hyperlink ref="A39" r:id="rId4" xr:uid="{1951B7F4-A0B3-4B65-AB72-634B8B744D75}"/>
-    <hyperlink ref="A45" r:id="rId5" xr:uid="{3A608E57-A37E-4B2F-8015-6F7230097DAF}"/>
-    <hyperlink ref="A46" r:id="rId6" xr:uid="{40E6C304-290C-475F-998C-F0DB68862CDE}"/>
-    <hyperlink ref="A54" r:id="rId7" xr:uid="{E65ABDBD-078E-473C-84D0-A6D6C236ACD4}"/>
-    <hyperlink ref="A67" r:id="rId8" xr:uid="{4510E958-8000-410B-BE05-76D3396BAFBE}"/>
-    <hyperlink ref="A73" r:id="rId9" xr:uid="{3969A9F3-CA56-4BB8-9892-597D2CBDFCE8}"/>
-    <hyperlink ref="A74" r:id="rId10" xr:uid="{6F8CA90A-474D-49C0-9A40-8B0805711B68}"/>
-    <hyperlink ref="A76" r:id="rId11" xr:uid="{00115D7E-9EDD-43F0-9114-C5CEE47E0872}"/>
-    <hyperlink ref="A77" r:id="rId12" xr:uid="{75C0C932-51C3-41C1-983F-58F27A9437E3}"/>
-    <hyperlink ref="A96" r:id="rId13" xr:uid="{FF0D6C28-D9CC-4562-9A0D-84346742E2DA}"/>
-    <hyperlink ref="A97" r:id="rId14" xr:uid="{5D80F0C2-4716-482F-A1ED-BF514804281D}"/>
-    <hyperlink ref="A116" r:id="rId15" xr:uid="{F44591C9-7EA3-4559-A7A6-B93E9C6EBBDD}"/>
-    <hyperlink ref="A117" r:id="rId16" xr:uid="{4C7F43D8-B100-4461-B8C3-C61284645D68}"/>
-    <hyperlink ref="A136" r:id="rId17" xr:uid="{73A6B1FA-71DA-427F-913B-02EE123619ED}"/>
-    <hyperlink ref="A139" r:id="rId18" xr:uid="{2E94DD8B-2784-4AFF-9BB6-0ED406D153B6}"/>
-    <hyperlink ref="A156" r:id="rId19" xr:uid="{3184DA50-7FFF-4983-BE22-7AD075B86520}"/>
-    <hyperlink ref="A159" r:id="rId20" xr:uid="{166658A0-4909-4882-9767-489DE86F0162}"/>
-    <hyperlink ref="A176" r:id="rId21" xr:uid="{454DEBF3-532F-4AF0-8730-37C0B4727220}"/>
-    <hyperlink ref="A179" r:id="rId22" xr:uid="{64B912CC-5831-4B4A-964B-CAE049145A1F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId23"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C42E093-990A-4D87-B497-B9D64E30A7FC}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D209"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4564,7 +5060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4578,7 +5074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -4592,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4606,7 +5102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4620,7 +5116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -4634,7 +5130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4648,7 +5144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -4662,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4676,7 +5172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -4690,7 +5186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -4704,7 +5200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
@@ -4718,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
@@ -4732,7 +5228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
@@ -4746,7 +5242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
@@ -4760,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
@@ -4774,8 +5270,2708 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="1">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="1">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="1">
+        <v>1</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" s="1">
+        <v>1</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>1</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" s="1">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="1">
+        <v>1</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" s="1">
+        <v>1</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85" s="1">
+        <v>1</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="1">
+        <v>1</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="1">
+        <v>1</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" s="1">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="1">
+        <v>1</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D90">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B91" s="1">
+        <v>1</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D91">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92" s="1">
+        <v>1</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D92">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B93" s="1">
+        <v>1</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D93">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" s="1">
+        <v>1</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D94">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="1">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1">
+        <v>1</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D96">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="1">
+        <v>1</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="1">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D102">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1">
+        <v>1</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="1">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D104">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="1">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="1">
+        <v>1</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1">
+        <v>1</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D107">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D108">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1">
+        <v>1</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D109">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" s="1">
+        <v>1</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D110">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B111" s="1">
+        <v>1</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B112" s="1">
+        <v>1</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B113" s="1">
+        <v>1</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D113">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B114" s="1">
+        <v>1</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D114">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B115" s="1">
+        <v>1</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D115">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B116" s="1">
+        <v>1</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D116">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B117" s="1">
+        <v>1</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D117">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B118" s="1">
+        <v>1</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B119" s="1">
+        <v>1</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D119">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B120" s="1">
+        <v>1</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D120">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="1">
+        <v>1</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B122" s="1">
+        <v>1</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D122">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B123" s="1">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D123">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B124" s="1">
+        <v>1</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B125" s="1">
+        <v>1</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D125">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B126" s="1">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D126">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B127" s="1">
+        <v>1</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D127">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B128" s="1">
+        <v>1</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B129" s="1">
+        <v>1</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D129">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B130" s="1">
+        <v>1</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D130">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B131" s="1">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D131">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B132" s="1">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D132">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B133" s="1">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D133">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B134" s="1">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D134">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B135" s="1">
+        <v>1</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D135">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B136" s="1">
+        <v>1</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D136">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B137" s="1">
+        <v>1</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D137">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B138" s="1">
+        <v>1</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D138">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B139" s="1">
+        <v>1</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D139">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B140" s="1">
+        <v>1</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D140">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B141" s="1">
+        <v>1</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B142" s="1">
+        <v>1</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D142">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B143" s="1">
+        <v>1</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D143">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B144" s="1">
+        <v>1</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D144">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B145" s="1">
+        <v>1</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D145">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B146" s="1">
+        <v>1</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D146">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B147" s="1">
+        <v>1</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D147">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B148" s="1">
+        <v>1</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D148">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B149" s="1">
+        <v>1</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D149">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B150" s="1">
+        <v>1</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D150">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B151" s="1">
+        <v>1</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D151">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B152" s="1">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B153" s="1">
+        <v>1</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D153">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B154" s="1">
+        <v>1</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D154">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B155" s="1">
+        <v>1</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D155">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B156" s="1">
+        <v>1</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D156">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B157" s="1">
+        <v>1</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D157">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158" s="1">
+        <v>1</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D158">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B159" s="1">
+        <v>1</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D159">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B160" s="1">
+        <v>1</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D160">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B161" s="1">
+        <v>1</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D161">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B162" s="1">
+        <v>1</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D162">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B163" s="1">
+        <v>1</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D163">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B164" s="1">
+        <v>1</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D164">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B165" s="1">
+        <v>1</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D165">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B166" s="1">
+        <v>1</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D166">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B167" s="1">
+        <v>1</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B168" s="1">
+        <v>1</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D168">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B169" s="1">
+        <v>1</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B170" s="1">
+        <v>1</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D170">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B171" s="1">
+        <v>1</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D171">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B172" s="1">
+        <v>1</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D172">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B173" s="1">
+        <v>1</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D173">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B174" s="1">
+        <v>1</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D174">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B175" s="1">
+        <v>1</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D175">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B176" s="1">
+        <v>1</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D176">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B177" s="1">
+        <v>1</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D177">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B178" s="1">
+        <v>1</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D178">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B179" s="1">
+        <v>1</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D179">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B180" s="1">
+        <v>1</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D180">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B181" s="1">
+        <v>1</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D181">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B182" s="1">
+        <v>1</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D182">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B183" s="1">
+        <v>1</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D183">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B184" s="1">
+        <v>1</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D184">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B185" s="1">
+        <v>1</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D185">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B186" s="1">
+        <v>1</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D186">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B187" s="1">
+        <v>1</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D187">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B188" s="1">
+        <v>1</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D188">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B189" s="1">
+        <v>1</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D189">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B190" s="1">
+        <v>1</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D190">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B191" s="1">
+        <v>1</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D191">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B192" s="1">
+        <v>1</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D192">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B193" s="1">
+        <v>1</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D193">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B194" s="1">
+        <v>1</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B195" s="1">
+        <v>1</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D195">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B196" s="1">
+        <v>1</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D196">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D197">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="1">
+        <v>1</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D198">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B199" s="1">
+        <v>1</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D199">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B200" s="1">
+        <v>1</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D200">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B201" s="1">
+        <v>1</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D201">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B202" s="1">
+        <v>1</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D202">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B203" s="1">
+        <v>1</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D203">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B204" s="1">
+        <v>1</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D204">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B205" s="1">
+        <v>1</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B206" s="1">
+        <v>1</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D206">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B207" s="1">
+        <v>1</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D207">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B208" s="1">
+        <v>1</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B209" s="1">
+        <v>1</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D209">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{64D4E90C-EBE7-4C7E-9ABA-D5574FA24707}"/>
@@ -4785,6 +7981,28 @@
     <hyperlink ref="A14" r:id="rId5" xr:uid="{7AFDDA0B-59A0-4E3E-B92C-7B82EA4F4B76}"/>
     <hyperlink ref="A15" r:id="rId6" xr:uid="{1CF315C4-B381-4080-95E8-1FFF21305804}"/>
     <hyperlink ref="A16" r:id="rId7" xr:uid="{B928BE1E-44ED-4F55-A7C2-1D621337ED19}"/>
+    <hyperlink ref="A39" r:id="rId8" xr:uid="{EC0A32D8-DF6A-4D72-AD75-AA06C555A6C9}"/>
+    <hyperlink ref="A45" r:id="rId9" xr:uid="{5C3D0804-5699-4DBF-B411-3C3A412B89AE}"/>
+    <hyperlink ref="A46" r:id="rId10" xr:uid="{F5980D0F-FAAA-4535-9BE9-1508C15687DF}"/>
+    <hyperlink ref="A54" r:id="rId11" xr:uid="{1951B7F4-A0B3-4B65-AB72-634B8B744D75}"/>
+    <hyperlink ref="A60" r:id="rId12" xr:uid="{3A608E57-A37E-4B2F-8015-6F7230097DAF}"/>
+    <hyperlink ref="A61" r:id="rId13" xr:uid="{40E6C304-290C-475F-998C-F0DB68862CDE}"/>
+    <hyperlink ref="A69" r:id="rId14" xr:uid="{E65ABDBD-078E-473C-84D0-A6D6C236ACD4}"/>
+    <hyperlink ref="A82" r:id="rId15" xr:uid="{4510E958-8000-410B-BE05-76D3396BAFBE}"/>
+    <hyperlink ref="A88" r:id="rId16" xr:uid="{3969A9F3-CA56-4BB8-9892-597D2CBDFCE8}"/>
+    <hyperlink ref="A89" r:id="rId17" xr:uid="{6F8CA90A-474D-49C0-9A40-8B0805711B68}"/>
+    <hyperlink ref="A91" r:id="rId18" xr:uid="{00115D7E-9EDD-43F0-9114-C5CEE47E0872}"/>
+    <hyperlink ref="A92" r:id="rId19" xr:uid="{75C0C932-51C3-41C1-983F-58F27A9437E3}"/>
+    <hyperlink ref="A111" r:id="rId20" xr:uid="{FF0D6C28-D9CC-4562-9A0D-84346742E2DA}"/>
+    <hyperlink ref="A112" r:id="rId21" xr:uid="{5D80F0C2-4716-482F-A1ED-BF514804281D}"/>
+    <hyperlink ref="A131" r:id="rId22" xr:uid="{F44591C9-7EA3-4559-A7A6-B93E9C6EBBDD}"/>
+    <hyperlink ref="A132" r:id="rId23" xr:uid="{4C7F43D8-B100-4461-B8C3-C61284645D68}"/>
+    <hyperlink ref="A151" r:id="rId24" xr:uid="{73A6B1FA-71DA-427F-913B-02EE123619ED}"/>
+    <hyperlink ref="A154" r:id="rId25" xr:uid="{2E94DD8B-2784-4AFF-9BB6-0ED406D153B6}"/>
+    <hyperlink ref="A171" r:id="rId26" xr:uid="{3184DA50-7FFF-4983-BE22-7AD075B86520}"/>
+    <hyperlink ref="A174" r:id="rId27" xr:uid="{166658A0-4909-4882-9767-489DE86F0162}"/>
+    <hyperlink ref="A191" r:id="rId28" xr:uid="{454DEBF3-532F-4AF0-8730-37C0B4727220}"/>
+    <hyperlink ref="A194" r:id="rId29" xr:uid="{64B912CC-5831-4B4A-964B-CAE049145A1F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
